--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2019_tarapaca.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:04</t>
+    <t xml:space="preserve">2026-09-24 00:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -681,13 +681,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>6</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="10">
@@ -727,13 +727,13 @@
         <v>6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="11">
@@ -744,19 +744,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.68</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="12">
@@ -796,13 +796,13 @@
         <v>6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.15</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>-0.06</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.45</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2019_tarapaca.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:55</t>
+    <t xml:space="preserve">2026-10-01 23:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2019_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezmat_a_2019_tarapaca.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:20</t>
+    <t xml:space="preserve">2026-10-05 19:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -825,7 +825,7 @@
         <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="15">
